--- a/セリフ編集/キャラ個人別/勝利セリフ.xlsx
+++ b/セリフ編集/キャラ個人別/勝利セリフ.xlsx
@@ -4690,19 +4690,19 @@
           <t xml:space="preserve">37[1]</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr" s="6">
+      <c r="E107" t="inlineStr" s="10">
         <is>
           <t xml:space="preserve">白銀麗子</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr" s="6">
+      <c r="F107" t="inlineStr" s="10">
         <is>
           <t xml:space="preserve">丁寧</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+      <c r="G107" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="H107" t="inlineStr" s="3">
@@ -4732,19 +4732,19 @@
           <t xml:space="preserve">37[2]</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr" s="6">
+      <c r="E108" t="inlineStr" s="10">
         <is>
           <t xml:space="preserve">白銀麗子</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr" s="6">
+      <c r="F108" t="inlineStr" s="10">
         <is>
           <t xml:space="preserve">丁寧</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+      <c r="G108" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="H108" t="inlineStr" s="3">
@@ -4774,19 +4774,19 @@
           <t xml:space="preserve">37[3]</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr" s="6">
+      <c r="E109" t="inlineStr" s="10">
         <is>
           <t xml:space="preserve">白銀麗子</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr" s="6">
+      <c r="F109" t="inlineStr" s="10">
         <is>
           <t xml:space="preserve">丁寧</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+      <c r="G109" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="H109" t="inlineStr" s="3">
@@ -6706,19 +6706,19 @@
           <t xml:space="preserve">53[1]</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr" s="5">
+      <c r="E155" t="inlineStr" s="9">
         <is>
           <t xml:space="preserve">小森さなえ</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr" s="5">
+      <c r="F155" t="inlineStr" s="9">
         <is>
           <t xml:space="preserve">標準</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+      <c r="G155" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="H155" t="inlineStr" s="3">
@@ -6748,19 +6748,19 @@
           <t xml:space="preserve">53[2]</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr" s="5">
+      <c r="E156" t="inlineStr" s="9">
         <is>
           <t xml:space="preserve">小森さなえ</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr" s="5">
+      <c r="F156" t="inlineStr" s="9">
         <is>
           <t xml:space="preserve">標準</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+      <c r="G156" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="H156" t="inlineStr" s="3">
@@ -6790,19 +6790,19 @@
           <t xml:space="preserve">53[3]</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr" s="5">
+      <c r="E157" t="inlineStr" s="9">
         <is>
           <t xml:space="preserve">小森さなえ</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr" s="5">
+      <c r="F157" t="inlineStr" s="9">
         <is>
           <t xml:space="preserve">標準</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+      <c r="G157" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="H157" t="inlineStr" s="3">
@@ -8344,19 +8344,19 @@
           <t xml:space="preserve">66[1]</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr" s="5">
+      <c r="E194" t="inlineStr" s="10">
         <is>
           <t xml:space="preserve">長谷川レオナ</t>
         </is>
       </c>
-      <c r="F194" t="inlineStr" s="5">
+      <c r="F194" t="inlineStr" s="10">
         <is>
           <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+      <c r="G194" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="H194" t="inlineStr" s="3">
@@ -8386,19 +8386,19 @@
           <t xml:space="preserve">66[2]</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr" s="5">
+      <c r="E195" t="inlineStr" s="10">
         <is>
           <t xml:space="preserve">長谷川レオナ</t>
         </is>
       </c>
-      <c r="F195" t="inlineStr" s="5">
+      <c r="F195" t="inlineStr" s="10">
         <is>
           <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+      <c r="G195" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="H195" t="inlineStr" s="3">
@@ -8428,19 +8428,19 @@
           <t xml:space="preserve">66[3]</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr" s="5">
+      <c r="E196" t="inlineStr" s="10">
         <is>
           <t xml:space="preserve">長谷川レオナ</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr" s="5">
+      <c r="F196" t="inlineStr" s="10">
         <is>
           <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+      <c r="G196" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="H196" t="inlineStr" s="3">
@@ -9100,19 +9100,19 @@
           <t xml:space="preserve">72[1]</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr" s="5">
+      <c r="E212" t="inlineStr" s="9">
         <is>
           <t xml:space="preserve">穴澤ほのか</t>
         </is>
       </c>
-      <c r="F212" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">丁寧</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+      <c r="F212" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="H212" t="inlineStr" s="3">
@@ -9142,19 +9142,19 @@
           <t xml:space="preserve">72[2]</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr" s="5">
+      <c r="E213" t="inlineStr" s="9">
         <is>
           <t xml:space="preserve">穴澤ほのか</t>
         </is>
       </c>
-      <c r="F213" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">丁寧</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+      <c r="F213" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="H213" t="inlineStr" s="3">
@@ -9184,19 +9184,19 @@
           <t xml:space="preserve">72[3]</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr" s="5">
+      <c r="E214" t="inlineStr" s="9">
         <is>
           <t xml:space="preserve">穴澤ほのか</t>
         </is>
       </c>
-      <c r="F214" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">丁寧</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+      <c r="F214" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="H214" t="inlineStr" s="3">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="F221" t="inlineStr" s="9">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G221" t="inlineStr" s="9">
@@ -9527,7 +9527,7 @@
       </c>
       <c r="F222" t="inlineStr" s="9">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G222" t="inlineStr" s="9">
@@ -9569,7 +9569,7 @@
       </c>
       <c r="F223" t="inlineStr" s="9">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G223" t="inlineStr" s="9">
@@ -10612,19 +10612,19 @@
           <t xml:space="preserve">84[1]</t>
         </is>
       </c>
-      <c r="E248" t="inlineStr" s="6">
+      <c r="E248" t="inlineStr" s="5">
         <is>
           <t xml:space="preserve">南谷杏</t>
         </is>
       </c>
-      <c r="F248" t="inlineStr" s="6">
+      <c r="F248" t="inlineStr" s="5">
         <is>
           <t xml:space="preserve">標準</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+      <c r="G248" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="H248" t="inlineStr" s="3">
@@ -10654,19 +10654,19 @@
           <t xml:space="preserve">84[2]</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr" s="6">
+      <c r="E249" t="inlineStr" s="5">
         <is>
           <t xml:space="preserve">南谷杏</t>
         </is>
       </c>
-      <c r="F249" t="inlineStr" s="6">
+      <c r="F249" t="inlineStr" s="5">
         <is>
           <t xml:space="preserve">標準</t>
         </is>
       </c>
-      <c r="G249" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+      <c r="G249" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="H249" t="inlineStr" s="3">
@@ -10696,19 +10696,19 @@
           <t xml:space="preserve">84[3]</t>
         </is>
       </c>
-      <c r="E250" t="inlineStr" s="6">
+      <c r="E250" t="inlineStr" s="5">
         <is>
           <t xml:space="preserve">南谷杏</t>
         </is>
       </c>
-      <c r="F250" t="inlineStr" s="6">
+      <c r="F250" t="inlineStr" s="5">
         <is>
           <t xml:space="preserve">標準</t>
         </is>
       </c>
-      <c r="G250" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+      <c r="G250" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="H250" t="inlineStr" s="3">
@@ -13510,19 +13510,19 @@
           <t xml:space="preserve">107[1]</t>
         </is>
       </c>
-      <c r="E317" t="inlineStr" s="5">
+      <c r="E317" t="inlineStr" s="8">
         <is>
           <t xml:space="preserve">松岡綾乃</t>
         </is>
       </c>
-      <c r="F317" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">クール</t>
-        </is>
-      </c>
-      <c r="G317" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+      <c r="F317" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">丁寧</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="H317" t="inlineStr" s="3">
@@ -13552,19 +13552,19 @@
           <t xml:space="preserve">107[2]</t>
         </is>
       </c>
-      <c r="E318" t="inlineStr" s="5">
+      <c r="E318" t="inlineStr" s="8">
         <is>
           <t xml:space="preserve">松岡綾乃</t>
         </is>
       </c>
-      <c r="F318" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">クール</t>
-        </is>
-      </c>
-      <c r="G318" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+      <c r="F318" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">丁寧</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="H318" t="inlineStr" s="3">
@@ -13594,19 +13594,19 @@
           <t xml:space="preserve">107[3]</t>
         </is>
       </c>
-      <c r="E319" t="inlineStr" s="5">
+      <c r="E319" t="inlineStr" s="8">
         <is>
           <t xml:space="preserve">松岡綾乃</t>
         </is>
       </c>
-      <c r="F319" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">クール</t>
-        </is>
-      </c>
-      <c r="G319" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+      <c r="F319" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">丁寧</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="H319" t="inlineStr" s="3">
@@ -15274,19 +15274,19 @@
           <t xml:space="preserve">121[1]</t>
         </is>
       </c>
-      <c r="E359" t="inlineStr" s="5">
+      <c r="E359" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">山本理香</t>
         </is>
       </c>
-      <c r="F359" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
-        </is>
-      </c>
-      <c r="G359" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+      <c r="F359" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="H359" t="inlineStr" s="3">
@@ -15316,19 +15316,19 @@
           <t xml:space="preserve">121[2]</t>
         </is>
       </c>
-      <c r="E360" t="inlineStr" s="5">
+      <c r="E360" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">山本理香</t>
         </is>
       </c>
-      <c r="F360" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
-        </is>
-      </c>
-      <c r="G360" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+      <c r="F360" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="H360" t="inlineStr" s="3">
@@ -15358,19 +15358,19 @@
           <t xml:space="preserve">121[3]</t>
         </is>
       </c>
-      <c r="E361" t="inlineStr" s="5">
+      <c r="E361" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">山本理香</t>
         </is>
       </c>
-      <c r="F361" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
-        </is>
-      </c>
-      <c r="G361" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+      <c r="F361" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="H361" t="inlineStr" s="3">
